--- a/modelo_dados_portfolio.xlsx
+++ b/modelo_dados_portfolio.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Criterios" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projetos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucoes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projetos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucoes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -85,10 +86,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -461,10 +465,10 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -513,7 +517,7 @@
           <t>VPL (R$ mil)</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="3" t="n">
         <v>0.35</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -523,16 +527,16 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
+          <t>Tipo 5 - Critério Linear com Indiferença (V-Shape with Indifference)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -542,7 +546,7 @@
           <t>Alinhamento Estratégico (1-5)</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -552,16 +556,16 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
+          <t>Tipo 3 - Critério Linear (V-Shape)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -571,7 +575,7 @@
           <t>Risco de Execução (1-5)</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -581,16 +585,16 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>usual</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
+          <t>Tipo 1 - Critério Usual</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -600,7 +604,7 @@
           <t>Impacto ESG (1-5)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3" t="n">
         <v>0.15</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -610,17 +614,78 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>linear</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
+          <t>Tipo 3 - Critério Linear (V-Shape)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="3" t="n">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D50" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Função inválida" error="Escolha um dos 6 tipos da lista (Tipo 1 a Tipo 6)." type="list">
+      <formula1>=Listas!$A$1:$A$6</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tipo 1 - Critério Usual</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tipo 2 - Quasi-Critério (U-Shape)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tipo 3 - Critério Linear (V-Shape)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Tipo 4 - Critério de Nível</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tipo 5 - Critério Linear com Indiferença (V-Shape with Indifference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tipo 6 - Critério Gaussiano</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -628,7 +693,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -689,7 +754,7 @@
           <t>ERP Cloud</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="3" t="n">
         <v>1200</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -697,16 +762,16 @@
           <t>não</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -716,7 +781,7 @@
           <t>Nova Linha de Produção</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="3" t="n">
         <v>3500</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -724,16 +789,16 @@
           <t>não</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>2200</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -743,7 +808,7 @@
           <t>Expansão Nordeste</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="3" t="n">
         <v>2800</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -751,16 +816,16 @@
           <t>não</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -770,7 +835,7 @@
           <t>Programa ESG</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3" t="n">
         <v>800</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -778,16 +843,16 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -797,7 +862,7 @@
           <t>Automação Logística</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="3" t="n">
         <v>1500</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -805,16 +870,16 @@
           <t>não</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>1100</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -824,7 +889,7 @@
           <t>CRM Comercial</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="3" t="n">
         <v>600</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -832,16 +897,16 @@
           <t>não</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>450</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -851,7 +916,7 @@
           <t>Eficiência Energética</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="3" t="n">
         <v>900</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -859,16 +924,16 @@
           <t>não</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -878,7 +943,7 @@
           <t>Data Analytics</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="3" t="n">
         <v>700</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -886,16 +951,16 @@
           <t>não</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -904,169 +969,176 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="130" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>COMO PREENCHER ESTA PLANILHA</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr"/>
+      <c r="A2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Aba CRITERIOS — os critérios de decisão derivados do seu planejamento estratégico (ex.: perspectivas do BSC):</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Peso: importância relativa do critério (o app normaliza para somar 1,00).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Objetivo: 'max' se quanto maior melhor (VPL, alinhamento); 'min' se quanto menor melhor (risco).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • FuncaoPreferencia: um dos 6 tipos de Brans, Vincke &amp; Mareschal (1986):</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • FuncaoPreferencia: escolha na lista suspensa um dos 6 tipos de Brans, Vincke &amp; Mareschal (1986):</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - usual      (Tipo 1): qualquer diferença positiva gera preferência total. Sem parâmetros.</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - Tipo 1 - Critério Usual (Usual criterion): qualquer diferença positiva gera preferência total. Sem parâmetros.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - u-shape    (Tipo 2): indiferente até q; preferência total acima de q. Usa: q_indiferenca.</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - Tipo 2 - Quasi-Critério (U-Shape) (Quasi criterion): indiferente até q; preferência total acima de q. Usa: q_indiferenca.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - v-shape    (Tipo 3): preferência cresce linearmente de 0 até p (P = d/p). Usa: p_preferencia.</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - Tipo 3 - Critério Linear (V-Shape) (Linear criterion): preferência cresce linearmente de 0 até p (P = d/p). Usa: p_preferencia.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - level      (Tipo 4): 0 até q; 1/2 entre q e p; 1 acima de p. Usa: q_indiferenca e p_preferencia (p &gt; q).</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - Tipo 4 - Critério de Nível (Level criterion): 0 até q; 1/2 entre q e p; 1 acima de p. Usa: q_indiferenca e p_preferencia (p &gt; q).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - linear     (Tipo 5): 0 até q; cresce linearmente entre q e p (P = (d-q)/(p-q)); 1 acima de p. Usa: q e p.</t>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - Tipo 5 - Critério Linear com Indiferença (V-Shape with Indifference) (Linear with indifference): 0 até q; cresce linearmente entre q e p (P = (d-q)/(p-q)); 1 acima de p. Usa: q e p.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      - gaussiana  (Tipo 6): crescimento suave P = 1 - exp(-d²/2s²). Usa: s_gaussiana.</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      - Tipo 6 - Critério Gaussiano (Gaussian criterion): crescimento suave P = 1 - exp(-d²/2s²). Usa: s_gaussiana.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • q_indiferenca: limiar de indiferença — usado por u-shape, level e linear (deixe 0 nos demais tipos).</t>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • q_indiferenca: limiar de indiferença — usado pelos Tipos 2, 4 e 5 (deixe 0 nos demais).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • p_preferencia: limiar de preferência total — usado por v-shape, level e linear (deixe 0 nos demais).</t>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • p_preferencia: limiar de preferência total — usado pelos Tipos 3, 4 e 5 (deixe 0 nos demais).</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • s_gaussiana: ponto de inflexão s — usado apenas pela gaussiana (deixe 0 nos demais).</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • s_gaussiana: ponto de inflexão s — usado apenas pelo Tipo 6 (deixe 0 nos demais).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Se um parâmetro exigido ficar em 0, o app avisa e trata a função como 'usual'.</t>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Também é aceito escrever apenas 'Tipo 1' ... 'Tipo 6'. Parâmetro exigido deixado em 0 faz a função</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr"/>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    degradar para o Critério Usual (o app avisa na tela).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Aba PROJETOS — uma linha por projeto candidato:</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Custo: investimento requerido, na MESMA unidade do orçamento informado no app (ex.: R$ mil).</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Obrigatorio: 'sim' para projetos mandatórios (regulatórios, segurança) — entram na carteira antes da otimização.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  • Colunas de desempenho: uma para cada critério, com nome IDÊNTICO ao da aba Criterios.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr"/>
-    </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>No app: faça o upload desta planilha, informe o orçamento total e navegue pelas abas de resultado.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Método: PROMETHEE II (ranking) + PROMETHEE V (carteira ótima sob restrição orçamentária).</t>
         </is>
